--- a/src/outputs/fs-ta_schedule-final.xlsx
+++ b/src/outputs/fs-ta_schedule-final.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84F25CD-771E-44C6-AB43-906C45AE6F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="TA Schedule" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sessions Count" state="visible" r:id="rId5"/>
+    <sheet name="TA Schedule" sheetId="1" r:id="rId1"/>
+    <sheet name="Sessions Count" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -782,14 +786,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1152,16 +1156,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D906"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="1" max="1" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1203,7 +1208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1217,7 +1222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1245,7 +1250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1259,7 +1264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1273,7 +1278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1287,7 +1292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1301,7 +1306,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1315,7 +1320,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1329,7 +1334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1343,7 +1348,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1357,7 +1362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1371,7 +1376,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1385,7 +1390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1399,7 +1404,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1413,7 +1418,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1427,7 +1432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1441,7 +1446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1455,7 +1460,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1469,7 +1474,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1483,7 +1488,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1497,7 +1502,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1511,7 +1516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1525,7 +1530,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1539,7 +1544,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1553,7 +1558,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1567,7 +1572,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1581,7 +1586,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1595,7 +1600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1609,7 +1614,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1623,7 +1628,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1637,7 +1642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1651,7 +1656,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1665,7 +1670,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1679,7 +1684,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1693,7 +1698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1707,7 +1712,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1721,7 +1726,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1735,7 +1740,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1749,7 +1754,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1763,7 +1768,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1777,7 +1782,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1791,7 +1796,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1805,7 +1810,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1819,7 +1824,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1833,7 +1838,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1847,7 +1852,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1861,7 +1866,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1875,7 +1880,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1889,7 +1894,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -1903,7 +1908,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1917,7 +1922,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1931,7 +1936,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1945,7 +1950,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -1959,7 +1964,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1973,7 +1978,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1987,7 +1992,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -2001,7 +2006,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -2015,7 +2020,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -2029,7 +2034,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -2043,7 +2048,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -2057,7 +2062,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>92</v>
       </c>
@@ -2071,7 +2076,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>92</v>
       </c>
@@ -2085,7 +2090,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>92</v>
       </c>
@@ -2099,7 +2104,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>92</v>
       </c>
@@ -2113,7 +2118,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>92</v>
       </c>
@@ -2127,7 +2132,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -2141,7 +2146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>92</v>
       </c>
@@ -2155,7 +2160,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -2169,7 +2174,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>92</v>
       </c>
@@ -2183,7 +2188,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>92</v>
       </c>
@@ -2197,7 +2202,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -2211,7 +2216,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>92</v>
       </c>
@@ -2225,7 +2230,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -2239,7 +2244,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -2253,7 +2258,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2267,7 +2272,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -2281,7 +2286,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -2295,7 +2300,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -2309,7 +2314,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>92</v>
       </c>
@@ -2323,7 +2328,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -2337,7 +2342,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -2351,7 +2356,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2365,7 +2370,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -2379,7 +2384,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -2393,7 +2398,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2407,7 +2412,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -2421,7 +2426,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>92</v>
       </c>
@@ -2435,7 +2440,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>92</v>
       </c>
@@ -2449,7 +2454,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -2463,7 +2468,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -2477,7 +2482,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>92</v>
       </c>
@@ -2491,7 +2496,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>92</v>
       </c>
@@ -2505,7 +2510,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>92</v>
       </c>
@@ -2519,7 +2524,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>92</v>
       </c>
@@ -2533,7 +2538,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>92</v>
       </c>
@@ -2547,7 +2552,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>92</v>
       </c>
@@ -2561,7 +2566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>92</v>
       </c>
@@ -2575,7 +2580,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>92</v>
       </c>
@@ -2589,7 +2594,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>92</v>
       </c>
@@ -2603,7 +2608,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>92</v>
       </c>
@@ -2617,7 +2622,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>92</v>
       </c>
@@ -2631,7 +2636,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>92</v>
       </c>
@@ -2645,7 +2650,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>92</v>
       </c>
@@ -2659,7 +2664,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>92</v>
       </c>
@@ -2673,7 +2678,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>92</v>
       </c>
@@ -2687,7 +2692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>92</v>
       </c>
@@ -2701,7 +2706,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>92</v>
       </c>
@@ -2715,7 +2720,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>92</v>
       </c>
@@ -2729,7 +2734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>92</v>
       </c>
@@ -2743,7 +2748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>92</v>
       </c>
@@ -2757,7 +2762,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>92</v>
       </c>
@@ -2771,7 +2776,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>92</v>
       </c>
@@ -2785,7 +2790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>92</v>
       </c>
@@ -2799,7 +2804,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>92</v>
       </c>
@@ -2813,7 +2818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -2827,7 +2832,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>92</v>
       </c>
@@ -2841,7 +2846,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -2855,7 +2860,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -2869,7 +2874,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>92</v>
       </c>
@@ -2883,7 +2888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>92</v>
       </c>
@@ -2897,7 +2902,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>92</v>
       </c>
@@ -2911,7 +2916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>92</v>
       </c>
@@ -2925,7 +2930,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>92</v>
       </c>
@@ -2939,7 +2944,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>143</v>
       </c>
@@ -2953,7 +2958,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>143</v>
       </c>
@@ -2967,7 +2972,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>143</v>
       </c>
@@ -2981,7 +2986,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>143</v>
       </c>
@@ -2995,7 +3000,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>143</v>
       </c>
@@ -3009,7 +3014,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -3023,7 +3028,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -3037,7 +3042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -3051,7 +3056,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>143</v>
       </c>
@@ -3065,7 +3070,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -3079,7 +3084,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -3093,7 +3098,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -3107,7 +3112,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -3121,7 +3126,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>143</v>
       </c>
@@ -3135,7 +3140,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>143</v>
       </c>
@@ -3149,7 +3154,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>143</v>
       </c>
@@ -3163,7 +3168,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>143</v>
       </c>
@@ -3177,7 +3182,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>143</v>
       </c>
@@ -3191,7 +3196,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>143</v>
       </c>
@@ -3205,7 +3210,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>143</v>
       </c>
@@ -3219,7 +3224,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>143</v>
       </c>
@@ -3233,7 +3238,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>143</v>
       </c>
@@ -3247,7 +3252,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>143</v>
       </c>
@@ -3261,7 +3266,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>143</v>
       </c>
@@ -3275,7 +3280,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>143</v>
       </c>
@@ -3289,7 +3294,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>143</v>
       </c>
@@ -3303,7 +3308,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>143</v>
       </c>
@@ -3317,7 +3322,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>143</v>
       </c>
@@ -3331,7 +3336,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>143</v>
       </c>
@@ -3345,7 +3350,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>143</v>
       </c>
@@ -3359,7 +3364,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>143</v>
       </c>
@@ -3373,7 +3378,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>143</v>
       </c>
@@ -3387,7 +3392,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>143</v>
       </c>
@@ -3401,7 +3406,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>143</v>
       </c>
@@ -3415,7 +3420,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>143</v>
       </c>
@@ -3429,7 +3434,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>143</v>
       </c>
@@ -3443,7 +3448,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>143</v>
       </c>
@@ -3457,7 +3462,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>143</v>
       </c>
@@ -3471,7 +3476,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>143</v>
       </c>
@@ -3485,7 +3490,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>143</v>
       </c>
@@ -3499,7 +3504,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>143</v>
       </c>
@@ -3513,7 +3518,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>143</v>
       </c>
@@ -3527,7 +3532,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>143</v>
       </c>
@@ -3541,7 +3546,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>143</v>
       </c>
@@ -3555,7 +3560,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>143</v>
       </c>
@@ -3569,7 +3574,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>143</v>
       </c>
@@ -3583,7 +3588,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>143</v>
       </c>
@@ -3597,7 +3602,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>143</v>
       </c>
@@ -3611,7 +3616,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>143</v>
       </c>
@@ -3625,7 +3630,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>143</v>
       </c>
@@ -3639,7 +3644,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>143</v>
       </c>
@@ -3653,7 +3658,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>143</v>
       </c>
@@ -3667,7 +3672,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>143</v>
       </c>
@@ -3681,7 +3686,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>143</v>
       </c>
@@ -3695,7 +3700,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>143</v>
       </c>
@@ -3709,7 +3714,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>143</v>
       </c>
@@ -3723,7 +3728,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>143</v>
       </c>
@@ -3737,7 +3742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>143</v>
       </c>
@@ -3751,7 +3756,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>143</v>
       </c>
@@ -3765,7 +3770,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>143</v>
       </c>
@@ -3779,7 +3784,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>143</v>
       </c>
@@ -3793,7 +3798,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>169</v>
       </c>
@@ -3807,7 +3812,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>169</v>
       </c>
@@ -3821,7 +3826,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>169</v>
       </c>
@@ -3835,7 +3840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>169</v>
       </c>
@@ -3849,7 +3854,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>169</v>
       </c>
@@ -3863,7 +3868,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>169</v>
       </c>
@@ -3877,7 +3882,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>169</v>
       </c>
@@ -3891,7 +3896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>169</v>
       </c>
@@ -3905,7 +3910,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>169</v>
       </c>
@@ -3919,7 +3924,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>169</v>
       </c>
@@ -3933,7 +3938,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>169</v>
       </c>
@@ -3947,7 +3952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>169</v>
       </c>
@@ -3961,7 +3966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>169</v>
       </c>
@@ -3975,7 +3980,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>169</v>
       </c>
@@ -3989,7 +3994,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>169</v>
       </c>
@@ -4003,7 +4008,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>169</v>
       </c>
@@ -4017,7 +4022,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>169</v>
       </c>
@@ -4031,7 +4036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>169</v>
       </c>
@@ -4045,7 +4050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>169</v>
       </c>
@@ -4059,7 +4064,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>169</v>
       </c>
@@ -4073,7 +4078,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>169</v>
       </c>
@@ -4087,7 +4092,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>169</v>
       </c>
@@ -4101,7 +4106,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>169</v>
       </c>
@@ -4115,7 +4120,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>169</v>
       </c>
@@ -4129,7 +4134,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>169</v>
       </c>
@@ -4143,7 +4148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>169</v>
       </c>
@@ -4157,7 +4162,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>169</v>
       </c>
@@ -4171,7 +4176,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>169</v>
       </c>
@@ -4185,7 +4190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>169</v>
       </c>
@@ -4199,7 +4204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>169</v>
       </c>
@@ -4213,7 +4218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>169</v>
       </c>
@@ -4227,7 +4232,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>169</v>
       </c>
@@ -4241,7 +4246,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>169</v>
       </c>
@@ -4255,7 +4260,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>169</v>
       </c>
@@ -4269,7 +4274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>169</v>
       </c>
@@ -4283,7 +4288,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>169</v>
       </c>
@@ -4297,7 +4302,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>169</v>
       </c>
@@ -4311,7 +4316,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>169</v>
       </c>
@@ -4325,7 +4330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>169</v>
       </c>
@@ -4339,7 +4344,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>169</v>
       </c>
@@ -4353,7 +4358,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>169</v>
       </c>
@@ -4367,7 +4372,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>169</v>
       </c>
@@ -4381,7 +4386,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>169</v>
       </c>
@@ -4395,7 +4400,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>169</v>
       </c>
@@ -4409,7 +4414,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>169</v>
       </c>
@@ -4423,7 +4428,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>169</v>
       </c>
@@ -4437,7 +4442,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>169</v>
       </c>
@@ -4451,7 +4456,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>169</v>
       </c>
@@ -4465,7 +4470,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>169</v>
       </c>
@@ -4479,7 +4484,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>169</v>
       </c>
@@ -4493,7 +4498,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>169</v>
       </c>
@@ -4507,7 +4512,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>169</v>
       </c>
@@ -4521,7 +4526,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>169</v>
       </c>
@@ -4535,7 +4540,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>169</v>
       </c>
@@ -4549,7 +4554,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>169</v>
       </c>
@@ -4563,7 +4568,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>169</v>
       </c>
@@ -4577,7 +4582,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>169</v>
       </c>
@@ -4591,7 +4596,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>169</v>
       </c>
@@ -4605,7 +4610,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>169</v>
       </c>
@@ -4619,7 +4624,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>169</v>
       </c>
@@ -4633,7 +4638,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>169</v>
       </c>
@@ -4647,7 +4652,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>169</v>
       </c>
@@ -4661,7 +4666,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>169</v>
       </c>
@@ -4675,7 +4680,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>169</v>
       </c>
@@ -4689,7 +4694,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>183</v>
       </c>
@@ -4703,7 +4708,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>183</v>
       </c>
@@ -4717,7 +4722,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>183</v>
       </c>
@@ -4731,7 +4736,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>183</v>
       </c>
@@ -4745,7 +4750,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>183</v>
       </c>
@@ -4759,7 +4764,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>183</v>
       </c>
@@ -4773,7 +4778,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>183</v>
       </c>
@@ -4787,7 +4792,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>183</v>
       </c>
@@ -4801,7 +4806,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>183</v>
       </c>
@@ -4815,7 +4820,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>183</v>
       </c>
@@ -4829,7 +4834,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>183</v>
       </c>
@@ -4843,7 +4848,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>183</v>
       </c>
@@ -4857,7 +4862,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>183</v>
       </c>
@@ -4871,7 +4876,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>183</v>
       </c>
@@ -4885,7 +4890,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>183</v>
       </c>
@@ -4899,7 +4904,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>183</v>
       </c>
@@ -4913,7 +4918,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>183</v>
       </c>
@@ -4927,7 +4932,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>183</v>
       </c>
@@ -4941,7 +4946,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>183</v>
       </c>
@@ -4955,7 +4960,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>183</v>
       </c>
@@ -4969,7 +4974,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>183</v>
       </c>
@@ -4983,7 +4988,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>183</v>
       </c>
@@ -4997,7 +5002,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>183</v>
       </c>
@@ -5011,7 +5016,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>183</v>
       </c>
@@ -5025,7 +5030,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>183</v>
       </c>
@@ -5039,7 +5044,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>183</v>
       </c>
@@ -5053,7 +5058,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>183</v>
       </c>
@@ -5067,7 +5072,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>183</v>
       </c>
@@ -5081,7 +5086,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>183</v>
       </c>
@@ -5095,7 +5100,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>183</v>
       </c>
@@ -5109,7 +5114,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>183</v>
       </c>
@@ -5123,7 +5128,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>183</v>
       </c>
@@ -5137,7 +5142,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>183</v>
       </c>
@@ -5151,7 +5156,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>183</v>
       </c>
@@ -5165,7 +5170,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>183</v>
       </c>
@@ -5179,7 +5184,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>183</v>
       </c>
@@ -5193,7 +5198,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>183</v>
       </c>
@@ -5207,7 +5212,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>183</v>
       </c>
@@ -5221,7 +5226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>183</v>
       </c>
@@ -5235,7 +5240,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>183</v>
       </c>
@@ -5249,7 +5254,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>183</v>
       </c>
@@ -5263,7 +5268,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>183</v>
       </c>
@@ -5277,7 +5282,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>183</v>
       </c>
@@ -5291,7 +5296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>183</v>
       </c>
@@ -5305,7 +5310,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>183</v>
       </c>
@@ -5319,7 +5324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>183</v>
       </c>
@@ -5333,7 +5338,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>183</v>
       </c>
@@ -5347,7 +5352,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>183</v>
       </c>
@@ -5361,7 +5366,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>183</v>
       </c>
@@ -5375,7 +5380,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>183</v>
       </c>
@@ -5389,7 +5394,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>183</v>
       </c>
@@ -5403,7 +5408,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>183</v>
       </c>
@@ -5417,7 +5422,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>183</v>
       </c>
@@ -5431,7 +5436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>183</v>
       </c>
@@ -5445,7 +5450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>183</v>
       </c>
@@ -5459,7 +5464,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>183</v>
       </c>
@@ -5473,7 +5478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>183</v>
       </c>
@@ -5487,7 +5492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>183</v>
       </c>
@@ -5501,7 +5506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>183</v>
       </c>
@@ -5515,7 +5520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>183</v>
       </c>
@@ -5529,7 +5534,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>183</v>
       </c>
@@ -5543,7 +5548,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>183</v>
       </c>
@@ -5557,7 +5562,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>183</v>
       </c>
@@ -5571,7 +5576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>183</v>
       </c>
@@ -5585,7 +5590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>183</v>
       </c>
@@ -5599,7 +5604,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>198</v>
       </c>
@@ -5613,7 +5618,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>198</v>
       </c>
@@ -5627,7 +5632,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>198</v>
       </c>
@@ -5641,7 +5646,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>198</v>
       </c>
@@ -5655,7 +5660,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>198</v>
       </c>
@@ -5669,7 +5674,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>198</v>
       </c>
@@ -5683,7 +5688,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>198</v>
       </c>
@@ -5697,7 +5702,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>198</v>
       </c>
@@ -5711,7 +5716,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>198</v>
       </c>
@@ -5725,7 +5730,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>198</v>
       </c>
@@ -5739,7 +5744,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>198</v>
       </c>
@@ -5753,7 +5758,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>198</v>
       </c>
@@ -5767,7 +5772,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>198</v>
       </c>
@@ -5781,7 +5786,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>198</v>
       </c>
@@ -5795,7 +5800,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>198</v>
       </c>
@@ -5809,7 +5814,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>198</v>
       </c>
@@ -5823,7 +5828,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>198</v>
       </c>
@@ -5837,7 +5842,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>198</v>
       </c>
@@ -5851,7 +5856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>198</v>
       </c>
@@ -5865,7 +5870,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>198</v>
       </c>
@@ -5879,7 +5884,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>198</v>
       </c>
@@ -5893,7 +5898,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>198</v>
       </c>
@@ -5907,7 +5912,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>198</v>
       </c>
@@ -5921,7 +5926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>198</v>
       </c>
@@ -5935,7 +5940,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>198</v>
       </c>
@@ -5949,7 +5954,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>198</v>
       </c>
@@ -5963,7 +5968,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>198</v>
       </c>
@@ -5977,7 +5982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>198</v>
       </c>
@@ -5991,7 +5996,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>198</v>
       </c>
@@ -6005,7 +6010,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>198</v>
       </c>
@@ -6019,7 +6024,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>198</v>
       </c>
@@ -6033,7 +6038,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>198</v>
       </c>
@@ -6047,7 +6052,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>198</v>
       </c>
@@ -6061,7 +6066,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>198</v>
       </c>
@@ -6075,7 +6080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>198</v>
       </c>
@@ -6089,7 +6094,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>198</v>
       </c>
@@ -6103,7 +6108,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>198</v>
       </c>
@@ -6117,7 +6122,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>198</v>
       </c>
@@ -6131,7 +6136,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>198</v>
       </c>
@@ -6145,7 +6150,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>198</v>
       </c>
@@ -6159,7 +6164,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>198</v>
       </c>
@@ -6173,7 +6178,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>198</v>
       </c>
@@ -6187,7 +6192,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>198</v>
       </c>
@@ -6201,7 +6206,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>198</v>
       </c>
@@ -6215,7 +6220,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>198</v>
       </c>
@@ -6229,7 +6234,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>198</v>
       </c>
@@ -6243,7 +6248,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>198</v>
       </c>
@@ -6257,7 +6262,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>198</v>
       </c>
@@ -6271,7 +6276,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>198</v>
       </c>
@@ -6285,7 +6290,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>198</v>
       </c>
@@ -6299,7 +6304,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>198</v>
       </c>
@@ -6313,7 +6318,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>198</v>
       </c>
@@ -6327,7 +6332,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>198</v>
       </c>
@@ -6341,7 +6346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>198</v>
       </c>
@@ -6355,7 +6360,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>198</v>
       </c>
@@ -6369,7 +6374,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>198</v>
       </c>
@@ -6383,7 +6388,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>198</v>
       </c>
@@ -6397,7 +6402,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>198</v>
       </c>
@@ -6411,7 +6416,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>198</v>
       </c>
@@ -6425,7 +6430,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>198</v>
       </c>
@@ -6439,7 +6444,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>198</v>
       </c>
@@ -6453,7 +6458,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>198</v>
       </c>
@@ -6467,7 +6472,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>198</v>
       </c>
@@ -6481,7 +6486,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>198</v>
       </c>
@@ -6495,7 +6500,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>209</v>
       </c>
@@ -6509,7 +6514,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>209</v>
       </c>
@@ -6523,7 +6528,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>209</v>
       </c>
@@ -6537,7 +6542,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>209</v>
       </c>
@@ -6551,7 +6556,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>209</v>
       </c>
@@ -6565,7 +6570,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>209</v>
       </c>
@@ -6579,7 +6584,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>209</v>
       </c>
@@ -6593,7 +6598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>209</v>
       </c>
@@ -6607,7 +6612,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>209</v>
       </c>
@@ -6621,7 +6626,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>209</v>
       </c>
@@ -6635,7 +6640,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>209</v>
       </c>
@@ -6649,7 +6654,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>209</v>
       </c>
@@ -6663,7 +6668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>209</v>
       </c>
@@ -6677,7 +6682,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>209</v>
       </c>
@@ -6691,7 +6696,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>209</v>
       </c>
@@ -6705,7 +6710,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>209</v>
       </c>
@@ -6719,7 +6724,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>209</v>
       </c>
@@ -6733,7 +6738,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>209</v>
       </c>
@@ -6747,7 +6752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>209</v>
       </c>
@@ -6761,7 +6766,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>209</v>
       </c>
@@ -6775,7 +6780,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>209</v>
       </c>
@@ -6789,7 +6794,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>209</v>
       </c>
@@ -6803,7 +6808,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>209</v>
       </c>
@@ -6817,7 +6822,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>209</v>
       </c>
@@ -6831,7 +6836,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>209</v>
       </c>
@@ -6845,7 +6850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>209</v>
       </c>
@@ -6859,7 +6864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>209</v>
       </c>
@@ -6873,7 +6878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>209</v>
       </c>
@@ -6887,7 +6892,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>209</v>
       </c>
@@ -6901,7 +6906,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>209</v>
       </c>
@@ -6915,7 +6920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>209</v>
       </c>
@@ -6929,7 +6934,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>209</v>
       </c>
@@ -6943,7 +6948,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>209</v>
       </c>
@@ -6957,7 +6962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>209</v>
       </c>
@@ -6971,7 +6976,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>209</v>
       </c>
@@ -6985,7 +6990,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>209</v>
       </c>
@@ -6999,7 +7004,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>209</v>
       </c>
@@ -7013,7 +7018,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>209</v>
       </c>
@@ -7027,7 +7032,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>209</v>
       </c>
@@ -7041,7 +7046,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>209</v>
       </c>
@@ -7055,7 +7060,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>209</v>
       </c>
@@ -7069,7 +7074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>209</v>
       </c>
@@ -7083,7 +7088,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>209</v>
       </c>
@@ -7097,7 +7102,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>209</v>
       </c>
@@ -7111,7 +7116,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>209</v>
       </c>
@@ -7125,7 +7130,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>209</v>
       </c>
@@ -7139,7 +7144,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>209</v>
       </c>
@@ -7153,7 +7158,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>209</v>
       </c>
@@ -7167,7 +7172,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>209</v>
       </c>
@@ -7181,7 +7186,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>209</v>
       </c>
@@ -7195,7 +7200,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>209</v>
       </c>
@@ -7209,7 +7214,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>209</v>
       </c>
@@ -7223,7 +7228,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>209</v>
       </c>
@@ -7237,7 +7242,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>209</v>
       </c>
@@ -7251,7 +7256,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>209</v>
       </c>
@@ -7265,7 +7270,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>209</v>
       </c>
@@ -7279,7 +7284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>214</v>
       </c>
@@ -7293,7 +7298,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>214</v>
       </c>
@@ -7307,7 +7312,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>214</v>
       </c>
@@ -7321,7 +7326,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>214</v>
       </c>
@@ -7335,7 +7340,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>214</v>
       </c>
@@ -7349,7 +7354,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>214</v>
       </c>
@@ -7363,7 +7368,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>214</v>
       </c>
@@ -7377,7 +7382,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>214</v>
       </c>
@@ -7391,7 +7396,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>214</v>
       </c>
@@ -7405,7 +7410,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>214</v>
       </c>
@@ -7419,7 +7424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>214</v>
       </c>
@@ -7433,7 +7438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>214</v>
       </c>
@@ -7447,7 +7452,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>214</v>
       </c>
@@ -7461,7 +7466,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>214</v>
       </c>
@@ -7475,7 +7480,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>214</v>
       </c>
@@ -7489,7 +7494,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>214</v>
       </c>
@@ -7503,7 +7508,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>214</v>
       </c>
@@ -7517,7 +7522,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>214</v>
       </c>
@@ -7531,7 +7536,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>214</v>
       </c>
@@ -7545,7 +7550,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>214</v>
       </c>
@@ -7559,7 +7564,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>214</v>
       </c>
@@ -7573,7 +7578,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>214</v>
       </c>
@@ -7587,7 +7592,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>214</v>
       </c>
@@ -7601,7 +7606,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>214</v>
       </c>
@@ -7615,7 +7620,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>214</v>
       </c>
@@ -7629,7 +7634,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>214</v>
       </c>
@@ -7643,7 +7648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>214</v>
       </c>
@@ -7657,7 +7662,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>214</v>
       </c>
@@ -7671,7 +7676,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>214</v>
       </c>
@@ -7685,7 +7690,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>214</v>
       </c>
@@ -7699,7 +7704,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>214</v>
       </c>
@@ -7713,7 +7718,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>214</v>
       </c>
@@ -7727,7 +7732,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>214</v>
       </c>
@@ -7741,7 +7746,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>214</v>
       </c>
@@ -7755,7 +7760,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>214</v>
       </c>
@@ -7769,7 +7774,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>214</v>
       </c>
@@ -7783,7 +7788,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>214</v>
       </c>
@@ -7797,7 +7802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>214</v>
       </c>
@@ -7811,7 +7816,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>214</v>
       </c>
@@ -7825,7 +7830,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>214</v>
       </c>
@@ -7839,7 +7844,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>214</v>
       </c>
@@ -7853,7 +7858,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>214</v>
       </c>
@@ -7867,7 +7872,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>214</v>
       </c>
@@ -7881,7 +7886,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
         <v>214</v>
       </c>
@@ -7895,7 +7900,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
         <v>214</v>
       </c>
@@ -7909,7 +7914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
         <v>214</v>
       </c>
@@ -7923,7 +7928,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>214</v>
       </c>
@@ -7937,7 +7942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>214</v>
       </c>
@@ -7951,7 +7956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
         <v>214</v>
       </c>
@@ -7965,7 +7970,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
         <v>214</v>
       </c>
@@ -7979,7 +7984,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>214</v>
       </c>
@@ -7993,7 +7998,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>214</v>
       </c>
@@ -8007,7 +8012,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>214</v>
       </c>
@@ -8021,7 +8026,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>214</v>
       </c>
@@ -8035,7 +8040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>214</v>
       </c>
@@ -8049,7 +8054,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>214</v>
       </c>
@@ -8063,7 +8068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>214</v>
       </c>
@@ -8077,7 +8082,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>214</v>
       </c>
@@ -8091,7 +8096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>214</v>
       </c>
@@ -8105,7 +8110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>214</v>
       </c>
@@ -8119,7 +8124,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>214</v>
       </c>
@@ -8133,7 +8138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>214</v>
       </c>
@@ -8147,7 +8152,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>214</v>
       </c>
@@ -8161,7 +8166,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>214</v>
       </c>
@@ -8175,7 +8180,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>222</v>
       </c>
@@ -8189,7 +8194,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>222</v>
       </c>
@@ -8203,7 +8208,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>222</v>
       </c>
@@ -8217,7 +8222,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>222</v>
       </c>
@@ -8231,7 +8236,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>222</v>
       </c>
@@ -8245,7 +8250,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>222</v>
       </c>
@@ -8259,7 +8264,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>222</v>
       </c>
@@ -8273,7 +8278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
         <v>222</v>
       </c>
@@ -8287,7 +8292,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>222</v>
       </c>
@@ -8301,7 +8306,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>222</v>
       </c>
@@ -8315,7 +8320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>222</v>
       </c>
@@ -8329,7 +8334,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>222</v>
       </c>
@@ -8343,7 +8348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
         <v>222</v>
       </c>
@@ -8357,7 +8362,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>222</v>
       </c>
@@ -8371,7 +8376,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>222</v>
       </c>
@@ -8385,7 +8390,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>222</v>
       </c>
@@ -8399,7 +8404,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>222</v>
       </c>
@@ -8413,7 +8418,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
         <v>222</v>
       </c>
@@ -8427,7 +8432,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
         <v>222</v>
       </c>
@@ -8441,7 +8446,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>222</v>
       </c>
@@ -8455,7 +8460,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>222</v>
       </c>
@@ -8469,7 +8474,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>222</v>
       </c>
@@ -8483,7 +8488,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>222</v>
       </c>
@@ -8497,7 +8502,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>222</v>
       </c>
@@ -8511,7 +8516,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>222</v>
       </c>
@@ -8525,7 +8530,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>222</v>
       </c>
@@ -8539,7 +8544,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>222</v>
       </c>
@@ -8553,7 +8558,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>222</v>
       </c>
@@ -8567,7 +8572,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>222</v>
       </c>
@@ -8581,7 +8586,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>222</v>
       </c>
@@ -8595,7 +8600,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>222</v>
       </c>
@@ -8609,7 +8614,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>222</v>
       </c>
@@ -8623,7 +8628,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>222</v>
       </c>
@@ -8637,7 +8642,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>222</v>
       </c>
@@ -8651,7 +8656,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>222</v>
       </c>
@@ -8665,7 +8670,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>222</v>
       </c>
@@ -8679,7 +8684,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>222</v>
       </c>
@@ -8693,7 +8698,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>222</v>
       </c>
@@ -8707,7 +8712,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>222</v>
       </c>
@@ -8721,7 +8726,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>222</v>
       </c>
@@ -8735,7 +8740,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>222</v>
       </c>
@@ -8749,7 +8754,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>222</v>
       </c>
@@ -8763,7 +8768,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>222</v>
       </c>
@@ -8777,7 +8782,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>222</v>
       </c>
@@ -8791,7 +8796,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>222</v>
       </c>
@@ -8805,7 +8810,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>222</v>
       </c>
@@ -8819,7 +8824,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>222</v>
       </c>
@@ -8833,7 +8838,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>222</v>
       </c>
@@ -8847,7 +8852,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>222</v>
       </c>
@@ -8861,7 +8866,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>222</v>
       </c>
@@ -8875,7 +8880,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>222</v>
       </c>
@@ -8889,7 +8894,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>222</v>
       </c>
@@ -8903,7 +8908,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>222</v>
       </c>
@@ -8917,7 +8922,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>222</v>
       </c>
@@ -8931,7 +8936,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>222</v>
       </c>
@@ -8945,7 +8950,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>222</v>
       </c>
@@ -8959,7 +8964,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>222</v>
       </c>
@@ -8973,7 +8978,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>222</v>
       </c>
@@ -8987,7 +8992,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>222</v>
       </c>
@@ -9001,7 +9006,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>222</v>
       </c>
@@ -9015,7 +9020,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>222</v>
       </c>
@@ -9029,7 +9034,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>222</v>
       </c>
@@ -9043,7 +9048,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>222</v>
       </c>
@@ -9057,7 +9062,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>222</v>
       </c>
@@ -9071,7 +9076,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>222</v>
       </c>
@@ -9085,7 +9090,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>222</v>
       </c>
@@ -9099,7 +9104,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>222</v>
       </c>
@@ -9113,7 +9118,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>222</v>
       </c>
@@ -9127,7 +9132,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>222</v>
       </c>
@@ -9141,7 +9146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>222</v>
       </c>
@@ -9155,7 +9160,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>222</v>
       </c>
@@ -9169,7 +9174,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>229</v>
       </c>
@@ -9183,7 +9188,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>229</v>
       </c>
@@ -9197,7 +9202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>229</v>
       </c>
@@ -9211,7 +9216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>229</v>
       </c>
@@ -9225,7 +9230,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>229</v>
       </c>
@@ -9239,7 +9244,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>229</v>
       </c>
@@ -9253,7 +9258,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>229</v>
       </c>
@@ -9267,7 +9272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>229</v>
       </c>
@@ -9281,7 +9286,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>229</v>
       </c>
@@ -9295,7 +9300,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>229</v>
       </c>
@@ -9309,7 +9314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>229</v>
       </c>
@@ -9323,7 +9328,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>229</v>
       </c>
@@ -9337,7 +9342,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>229</v>
       </c>
@@ -9351,7 +9356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>229</v>
       </c>
@@ -9365,7 +9370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>229</v>
       </c>
@@ -9379,7 +9384,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>229</v>
       </c>
@@ -9393,7 +9398,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>229</v>
       </c>
@@ -9407,7 +9412,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>229</v>
       </c>
@@ -9421,7 +9426,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>229</v>
       </c>
@@ -9435,7 +9440,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>229</v>
       </c>
@@ -9449,7 +9454,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>229</v>
       </c>
@@ -9463,7 +9468,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>229</v>
       </c>
@@ -9477,7 +9482,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>229</v>
       </c>
@@ -9491,7 +9496,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>229</v>
       </c>
@@ -9505,7 +9510,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>229</v>
       </c>
@@ -9519,7 +9524,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>229</v>
       </c>
@@ -9533,7 +9538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>229</v>
       </c>
@@ -9547,7 +9552,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>229</v>
       </c>
@@ -9561,7 +9566,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>229</v>
       </c>
@@ -9575,7 +9580,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>229</v>
       </c>
@@ -9589,7 +9594,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>229</v>
       </c>
@@ -9603,7 +9608,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>229</v>
       </c>
@@ -9617,7 +9622,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>229</v>
       </c>
@@ -9631,7 +9636,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>229</v>
       </c>
@@ -9645,7 +9650,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>229</v>
       </c>
@@ -9659,7 +9664,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>229</v>
       </c>
@@ -9673,7 +9678,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>229</v>
       </c>
@@ -9687,7 +9692,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>229</v>
       </c>
@@ -9701,7 +9706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>229</v>
       </c>
@@ -9715,7 +9720,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>229</v>
       </c>
@@ -9729,7 +9734,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>229</v>
       </c>
@@ -9743,7 +9748,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>229</v>
       </c>
@@ -9757,7 +9762,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>229</v>
       </c>
@@ -9771,7 +9776,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>229</v>
       </c>
@@ -9785,7 +9790,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>229</v>
       </c>
@@ -9799,7 +9804,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>229</v>
       </c>
@@ -9813,7 +9818,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>229</v>
       </c>
@@ -9827,7 +9832,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>229</v>
       </c>
@@ -9841,7 +9846,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>229</v>
       </c>
@@ -9855,7 +9860,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>229</v>
       </c>
@@ -9869,7 +9874,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>229</v>
       </c>
@@ -9883,7 +9888,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>229</v>
       </c>
@@ -9897,7 +9902,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>229</v>
       </c>
@@ -9911,7 +9916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>229</v>
       </c>
@@ -9925,7 +9930,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>229</v>
       </c>
@@ -9939,7 +9944,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>229</v>
       </c>
@@ -9953,7 +9958,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>229</v>
       </c>
@@ -9967,7 +9972,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>229</v>
       </c>
@@ -9981,7 +9986,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>229</v>
       </c>
@@ -9995,7 +10000,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>229</v>
       </c>
@@ -10009,7 +10014,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>229</v>
       </c>
@@ -10023,7 +10028,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>235</v>
       </c>
@@ -10037,7 +10042,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>235</v>
       </c>
@@ -10051,7 +10056,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>235</v>
       </c>
@@ -10065,7 +10070,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>235</v>
       </c>
@@ -10079,7 +10084,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>235</v>
       </c>
@@ -10093,7 +10098,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>235</v>
       </c>
@@ -10107,7 +10112,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>235</v>
       </c>
@@ -10121,7 +10126,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>235</v>
       </c>
@@ -10135,7 +10140,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>235</v>
       </c>
@@ -10149,7 +10154,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>235</v>
       </c>
@@ -10163,7 +10168,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>235</v>
       </c>
@@ -10177,7 +10182,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>235</v>
       </c>
@@ -10191,7 +10196,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>235</v>
       </c>
@@ -10205,7 +10210,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>235</v>
       </c>
@@ -10219,7 +10224,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>235</v>
       </c>
@@ -10233,7 +10238,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>235</v>
       </c>
@@ -10247,7 +10252,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>235</v>
       </c>
@@ -10261,7 +10266,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>235</v>
       </c>
@@ -10275,7 +10280,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>235</v>
       </c>
@@ -10289,7 +10294,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>235</v>
       </c>
@@ -10303,7 +10308,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>235</v>
       </c>
@@ -10317,7 +10322,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>235</v>
       </c>
@@ -10331,7 +10336,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>235</v>
       </c>
@@ -10345,7 +10350,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>235</v>
       </c>
@@ -10359,7 +10364,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>235</v>
       </c>
@@ -10373,7 +10378,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>235</v>
       </c>
@@ -10387,7 +10392,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>235</v>
       </c>
@@ -10401,7 +10406,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>235</v>
       </c>
@@ -10415,7 +10420,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>235</v>
       </c>
@@ -10429,7 +10434,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>235</v>
       </c>
@@ -10443,7 +10448,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>235</v>
       </c>
@@ -10457,7 +10462,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>235</v>
       </c>
@@ -10471,7 +10476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>235</v>
       </c>
@@ -10485,7 +10490,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>235</v>
       </c>
@@ -10499,7 +10504,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>235</v>
       </c>
@@ -10513,7 +10518,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>235</v>
       </c>
@@ -10527,7 +10532,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>235</v>
       </c>
@@ -10541,7 +10546,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>235</v>
       </c>
@@ -10555,7 +10560,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>235</v>
       </c>
@@ -10569,7 +10574,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>235</v>
       </c>
@@ -10583,7 +10588,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>235</v>
       </c>
@@ -10597,7 +10602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>235</v>
       </c>
@@ -10611,7 +10616,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>235</v>
       </c>
@@ -10625,7 +10630,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>235</v>
       </c>
@@ -10639,7 +10644,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>235</v>
       </c>
@@ -10653,7 +10658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>235</v>
       </c>
@@ -10667,7 +10672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>235</v>
       </c>
@@ -10681,7 +10686,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>235</v>
       </c>
@@ -10695,7 +10700,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>235</v>
       </c>
@@ -10709,7 +10714,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>235</v>
       </c>
@@ -10723,7 +10728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>235</v>
       </c>
@@ -10737,7 +10742,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>235</v>
       </c>
@@ -10751,7 +10756,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>235</v>
       </c>
@@ -10765,7 +10770,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>235</v>
       </c>
@@ -10779,7 +10784,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>239</v>
       </c>
@@ -10793,7 +10798,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>239</v>
       </c>
@@ -10807,7 +10812,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>239</v>
       </c>
@@ -10821,7 +10826,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>239</v>
       </c>
@@ -10835,7 +10840,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>239</v>
       </c>
@@ -10849,7 +10854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>239</v>
       </c>
@@ -10863,7 +10868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>239</v>
       </c>
@@ -10877,7 +10882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>239</v>
       </c>
@@ -10891,7 +10896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>239</v>
       </c>
@@ -10905,7 +10910,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>239</v>
       </c>
@@ -10919,7 +10924,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>239</v>
       </c>
@@ -10933,7 +10938,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>239</v>
       </c>
@@ -10947,7 +10952,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>239</v>
       </c>
@@ -10961,7 +10966,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>239</v>
       </c>
@@ -10975,7 +10980,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>239</v>
       </c>
@@ -10989,7 +10994,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>239</v>
       </c>
@@ -11003,7 +11008,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>239</v>
       </c>
@@ -11017,7 +11022,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>239</v>
       </c>
@@ -11031,7 +11036,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>239</v>
       </c>
@@ -11045,7 +11050,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>239</v>
       </c>
@@ -11059,7 +11064,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>239</v>
       </c>
@@ -11073,7 +11078,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>239</v>
       </c>
@@ -11087,7 +11092,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>239</v>
       </c>
@@ -11101,7 +11106,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>239</v>
       </c>
@@ -11115,7 +11120,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>239</v>
       </c>
@@ -11129,7 +11134,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>239</v>
       </c>
@@ -11143,7 +11148,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>239</v>
       </c>
@@ -11157,7 +11162,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>239</v>
       </c>
@@ -11171,7 +11176,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>239</v>
       </c>
@@ -11185,7 +11190,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>239</v>
       </c>
@@ -11199,7 +11204,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>239</v>
       </c>
@@ -11213,7 +11218,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>239</v>
       </c>
@@ -11227,7 +11232,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>239</v>
       </c>
@@ -11241,7 +11246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>239</v>
       </c>
@@ -11255,7 +11260,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>239</v>
       </c>
@@ -11269,7 +11274,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>239</v>
       </c>
@@ -11283,7 +11288,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>239</v>
       </c>
@@ -11297,7 +11302,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>239</v>
       </c>
@@ -11311,7 +11316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>239</v>
       </c>
@@ -11325,7 +11330,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>239</v>
       </c>
@@ -11339,7 +11344,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>239</v>
       </c>
@@ -11353,7 +11358,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
         <v>239</v>
       </c>
@@ -11367,7 +11372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>239</v>
       </c>
@@ -11381,7 +11386,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>239</v>
       </c>
@@ -11395,7 +11400,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>239</v>
       </c>
@@ -11409,7 +11414,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>239</v>
       </c>
@@ -11423,7 +11428,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>239</v>
       </c>
@@ -11437,7 +11442,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>239</v>
       </c>
@@ -11451,7 +11456,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>239</v>
       </c>
@@ -11465,7 +11470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>239</v>
       </c>
@@ -11479,7 +11484,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>239</v>
       </c>
@@ -11493,7 +11498,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>239</v>
       </c>
@@ -11507,7 +11512,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>239</v>
       </c>
@@ -11521,7 +11526,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>239</v>
       </c>
@@ -11535,7 +11540,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
         <v>239</v>
       </c>
@@ -11549,7 +11554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>239</v>
       </c>
@@ -11563,7 +11568,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>239</v>
       </c>
@@ -11577,7 +11582,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>239</v>
       </c>
@@ -11591,7 +11596,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A782" t="s">
         <v>245</v>
       </c>
@@ -11605,7 +11610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
         <v>245</v>
       </c>
@@ -11619,7 +11624,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
         <v>245</v>
       </c>
@@ -11633,7 +11638,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
         <v>245</v>
       </c>
@@ -11647,7 +11652,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
         <v>245</v>
       </c>
@@ -11661,7 +11666,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
         <v>245</v>
       </c>
@@ -11675,7 +11680,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
         <v>245</v>
       </c>
@@ -11689,7 +11694,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
         <v>245</v>
       </c>
@@ -11703,7 +11708,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
         <v>245</v>
       </c>
@@ -11717,7 +11722,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="791" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
         <v>245</v>
       </c>
@@ -11731,7 +11736,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
         <v>245</v>
       </c>
@@ -11745,7 +11750,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="793" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
         <v>245</v>
       </c>
@@ -11759,7 +11764,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
         <v>245</v>
       </c>
@@ -11773,7 +11778,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
         <v>245</v>
       </c>
@@ -11787,7 +11792,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
         <v>245</v>
       </c>
@@ -11801,7 +11806,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A797" t="s">
         <v>245</v>
       </c>
@@ -11815,7 +11820,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="798" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
         <v>245</v>
       </c>
@@ -11829,7 +11834,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="799" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
         <v>245</v>
       </c>
@@ -11843,7 +11848,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A800" t="s">
         <v>245</v>
       </c>
@@ -11857,7 +11862,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A801" t="s">
         <v>245</v>
       </c>
@@ -11871,7 +11876,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A802" t="s">
         <v>245</v>
       </c>
@@ -11885,7 +11890,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A803" t="s">
         <v>245</v>
       </c>
@@ -11899,7 +11904,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A805" t="s">
         <v>245</v>
       </c>
@@ -11913,7 +11918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A806" t="s">
         <v>245</v>
       </c>
@@ -11927,7 +11932,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A807" t="s">
         <v>245</v>
       </c>
@@ -11941,7 +11946,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="808" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A808" t="s">
         <v>245</v>
       </c>
@@ -11955,7 +11960,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="809" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A809" t="s">
         <v>245</v>
       </c>
@@ -11969,7 +11974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="810" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A810" t="s">
         <v>245</v>
       </c>
@@ -11983,7 +11988,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="811" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
         <v>245</v>
       </c>
@@ -11997,7 +12002,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="812" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
         <v>245</v>
       </c>
@@ -12011,7 +12016,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="813" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
         <v>245</v>
       </c>
@@ -12025,7 +12030,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="814" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
         <v>245</v>
       </c>
@@ -12039,7 +12044,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="815" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
         <v>245</v>
       </c>
@@ -12053,7 +12058,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
         <v>245</v>
       </c>
@@ -12067,7 +12072,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="817" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
         <v>245</v>
       </c>
@@ -12081,7 +12086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="818" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
         <v>245</v>
       </c>
@@ -12095,7 +12100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="819" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
         <v>245</v>
       </c>
@@ -12109,7 +12114,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="820" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
         <v>245</v>
       </c>
@@ -12123,7 +12128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="821" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A821" t="s">
         <v>245</v>
       </c>
@@ -12137,7 +12142,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="822" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
         <v>245</v>
       </c>
@@ -12151,7 +12156,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="823" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A823" t="s">
         <v>245</v>
       </c>
@@ -12165,7 +12170,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="824" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A824" t="s">
         <v>245</v>
       </c>
@@ -12179,7 +12184,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="826" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A826" t="s">
         <v>245</v>
       </c>
@@ -12193,7 +12198,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A827" t="s">
         <v>245</v>
       </c>
@@ -12207,7 +12212,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="828" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A828" t="s">
         <v>245</v>
       </c>
@@ -12221,7 +12226,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A829" t="s">
         <v>245</v>
       </c>
@@ -12235,7 +12240,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="830" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A830" t="s">
         <v>245</v>
       </c>
@@ -12249,7 +12254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="831" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A831" t="s">
         <v>245</v>
       </c>
@@ -12263,7 +12268,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="832" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A832" t="s">
         <v>245</v>
       </c>
@@ -12277,7 +12282,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="833" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A833" t="s">
         <v>245</v>
       </c>
@@ -12291,7 +12296,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="834" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A834" t="s">
         <v>245</v>
       </c>
@@ -12305,7 +12310,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="835" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A835" t="s">
         <v>245</v>
       </c>
@@ -12319,7 +12324,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="836" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A836" t="s">
         <v>245</v>
       </c>
@@ -12333,7 +12338,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="837" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A837" t="s">
         <v>245</v>
       </c>
@@ -12347,7 +12352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="838" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A838" t="s">
         <v>245</v>
       </c>
@@ -12361,7 +12366,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="839" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A839" t="s">
         <v>245</v>
       </c>
@@ -12375,7 +12380,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="840" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A840" t="s">
         <v>245</v>
       </c>
@@ -12389,7 +12394,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="841" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A841" t="s">
         <v>245</v>
       </c>
@@ -12403,7 +12408,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="842" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A842" t="s">
         <v>245</v>
       </c>
@@ -12417,7 +12422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="843" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A843" t="s">
         <v>245</v>
       </c>
@@ -12431,7 +12436,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="844" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A844" t="s">
         <v>245</v>
       </c>
@@ -12445,7 +12450,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="846" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A846" t="s">
         <v>251</v>
       </c>
@@ -12459,7 +12464,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="847" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A847" t="s">
         <v>251</v>
       </c>
@@ -12473,7 +12478,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="848" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A848" t="s">
         <v>251</v>
       </c>
@@ -12487,7 +12492,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="849" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A849" t="s">
         <v>251</v>
       </c>
@@ -12501,7 +12506,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="850" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A850" t="s">
         <v>251</v>
       </c>
@@ -12515,7 +12520,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="851" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A851" t="s">
         <v>251</v>
       </c>
@@ -12529,7 +12534,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="852" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A852" t="s">
         <v>251</v>
       </c>
@@ -12543,7 +12548,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="853" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A853" t="s">
         <v>251</v>
       </c>
@@ -12557,7 +12562,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="854" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A854" t="s">
         <v>251</v>
       </c>
@@ -12571,7 +12576,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="855" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
         <v>251</v>
       </c>
@@ -12585,7 +12590,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="856" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
         <v>251</v>
       </c>
@@ -12599,7 +12604,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="857" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
         <v>251</v>
       </c>
@@ -12613,7 +12618,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="858" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
         <v>251</v>
       </c>
@@ -12627,7 +12632,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="859" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
         <v>251</v>
       </c>
@@ -12641,7 +12646,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="860" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
         <v>251</v>
       </c>
@@ -12655,7 +12660,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="861" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
         <v>251</v>
       </c>
@@ -12669,7 +12674,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="862" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
         <v>251</v>
       </c>
@@ -12683,7 +12688,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="863" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
         <v>251</v>
       </c>
@@ -12697,7 +12702,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="864" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
         <v>251</v>
       </c>
@@ -12711,7 +12716,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="866" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A866" t="s">
         <v>251</v>
       </c>
@@ -12725,7 +12730,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="867" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A867" t="s">
         <v>251</v>
       </c>
@@ -12739,7 +12744,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="868" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A868" t="s">
         <v>251</v>
       </c>
@@ -12753,7 +12758,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="869" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A869" t="s">
         <v>251</v>
       </c>
@@ -12767,7 +12772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="870" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A870" t="s">
         <v>251</v>
       </c>
@@ -12781,7 +12786,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="871" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A871" t="s">
         <v>251</v>
       </c>
@@ -12795,7 +12800,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="872" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A872" t="s">
         <v>251</v>
       </c>
@@ -12809,7 +12814,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="873" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A873" t="s">
         <v>251</v>
       </c>
@@ -12823,7 +12828,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="874" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A874" t="s">
         <v>251</v>
       </c>
@@ -12837,7 +12842,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="875" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A875" t="s">
         <v>251</v>
       </c>
@@ -12851,7 +12856,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="876" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A876" t="s">
         <v>251</v>
       </c>
@@ -12865,7 +12870,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="877" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A877" t="s">
         <v>251</v>
       </c>
@@ -12879,7 +12884,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="878" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A878" t="s">
         <v>251</v>
       </c>
@@ -12893,7 +12898,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="879" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A879" t="s">
         <v>251</v>
       </c>
@@ -12907,7 +12912,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="880" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
         <v>251</v>
       </c>
@@ -12921,7 +12926,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="881" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A881" t="s">
         <v>251</v>
       </c>
@@ -12935,7 +12940,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="882" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
         <v>251</v>
       </c>
@@ -12949,7 +12954,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="883" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
         <v>251</v>
       </c>
@@ -12963,7 +12968,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A884" t="s">
         <v>251</v>
       </c>
@@ -12977,7 +12982,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A886" t="s">
         <v>251</v>
       </c>
@@ -12991,7 +12996,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A887" t="s">
         <v>251</v>
       </c>
@@ -13005,7 +13010,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="888" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A888" t="s">
         <v>251</v>
       </c>
@@ -13019,7 +13024,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="889" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A889" t="s">
         <v>251</v>
       </c>
@@ -13033,7 +13038,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="890" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A890" t="s">
         <v>251</v>
       </c>
@@ -13047,7 +13052,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A891" t="s">
         <v>251</v>
       </c>
@@ -13061,7 +13066,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="892" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A892" t="s">
         <v>251</v>
       </c>
@@ -13075,7 +13080,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A893" t="s">
         <v>251</v>
       </c>
@@ -13089,7 +13094,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A894" t="s">
         <v>251</v>
       </c>
@@ -13103,7 +13108,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="895" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A895" t="s">
         <v>251</v>
       </c>
@@ -13117,7 +13122,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="896" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A896" t="s">
         <v>251</v>
       </c>
@@ -13131,7 +13136,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="897" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A897" t="s">
         <v>251</v>
       </c>
@@ -13145,7 +13150,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="898" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A898" t="s">
         <v>251</v>
       </c>
@@ -13159,7 +13164,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="899" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A899" t="s">
         <v>251</v>
       </c>
@@ -13173,7 +13178,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="900" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A900" t="s">
         <v>251</v>
       </c>
@@ -13187,7 +13192,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="901" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A901" t="s">
         <v>251</v>
       </c>
@@ -13201,7 +13206,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="902" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A902" t="s">
         <v>251</v>
       </c>
@@ -13215,7 +13220,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="903" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A903" t="s">
         <v>251</v>
       </c>
@@ -13229,7 +13234,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="904" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A904" t="s">
         <v>251</v>
       </c>
@@ -13243,7 +13248,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="905" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A905" t="s">
         <v>251</v>
       </c>
@@ -13257,7 +13262,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="906" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A906" t="s">
         <v>251</v>
       </c>
@@ -13273,20 +13278,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B115"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>253</v>
       </c>
@@ -13294,7 +13299,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -13302,7 +13307,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -13310,7 +13315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>129</v>
       </c>
@@ -13318,7 +13323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>172</v>
       </c>
@@ -13326,7 +13331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -13334,7 +13339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13342,7 +13347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -13350,7 +13355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>126</v>
       </c>
@@ -13358,7 +13363,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -13366,7 +13371,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -13374,7 +13379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -13382,7 +13387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>128</v>
       </c>
@@ -13390,7 +13395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -13398,7 +13403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -13406,7 +13411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -13414,7 +13419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -13422,7 +13427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -13430,7 +13435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -13438,7 +13443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -13446,7 +13451,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -13454,7 +13459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -13462,7 +13467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -13470,7 +13475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -13478,7 +13483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -13486,7 +13491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -13494,7 +13499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -13502,7 +13507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -13510,7 +13515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -13518,7 +13523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -13526,7 +13531,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -13534,7 +13539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -13542,7 +13547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>57</v>
       </c>
@@ -13550,7 +13555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>138</v>
       </c>
@@ -13558,7 +13563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -13566,7 +13571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -13574,7 +13579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -13582,7 +13587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -13590,7 +13595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>144</v>
       </c>
@@ -13598,7 +13603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>152</v>
       </c>
@@ -13606,7 +13611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>64</v>
       </c>
@@ -13614,7 +13619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -13622,7 +13627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -13630,7 +13635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -13638,7 +13643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -13646,7 +13651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -13654,7 +13659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>145</v>
       </c>
@@ -13662,7 +13667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -13670,7 +13675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -13678,7 +13683,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -13686,7 +13691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -13694,7 +13699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -13702,7 +13707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>149</v>
       </c>
@@ -13710,7 +13715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>199</v>
       </c>
@@ -13718,7 +13723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>200</v>
       </c>
@@ -13726,7 +13731,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>85</v>
       </c>
@@ -13734,7 +13739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -13742,7 +13747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -13750,7 +13755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>179</v>
       </c>
@@ -13758,7 +13763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>180</v>
       </c>
@@ -13766,7 +13771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -13774,7 +13779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -13782,7 +13787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -13790,7 +13795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -13798,7 +13803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>71</v>
       </c>
@@ -13806,7 +13811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>157</v>
       </c>
@@ -13814,7 +13819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>156</v>
       </c>
@@ -13822,7 +13827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -13830,7 +13835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -13838,7 +13843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -13846,7 +13851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -13854,7 +13859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -13862,7 +13867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -13870,7 +13875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>80</v>
       </c>
@@ -13878,7 +13883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -13886,7 +13891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>97</v>
       </c>
@@ -13894,7 +13899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>98</v>
       </c>
@@ -13902,7 +13907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>111</v>
       </c>
@@ -13910,7 +13915,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -13918,7 +13923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -13926,7 +13931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -13934,7 +13939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>159</v>
       </c>
@@ -13942,7 +13947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>185</v>
       </c>
@@ -13950,7 +13955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>93</v>
       </c>
@@ -13958,7 +13963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -13966,7 +13971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -13974,7 +13979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -13982,7 +13987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -13990,7 +13995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -13998,7 +14003,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>106</v>
       </c>
@@ -14006,7 +14011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -14014,7 +14019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>108</v>
       </c>
@@ -14022,7 +14027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>109</v>
       </c>
@@ -14030,7 +14035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -14038,7 +14043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>107</v>
       </c>
@@ -14046,7 +14051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -14054,7 +14059,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>164</v>
       </c>
@@ -14062,7 +14067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>163</v>
       </c>
@@ -14070,7 +14075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -14078,7 +14083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>191</v>
       </c>
@@ -14086,7 +14091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -14094,7 +14099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -14102,7 +14107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>122</v>
       </c>
@@ -14110,7 +14115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>123</v>
       </c>
@@ -14118,7 +14123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>194</v>
       </c>
@@ -14126,7 +14131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>193</v>
       </c>
@@ -14134,7 +14139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>192</v>
       </c>
@@ -14142,7 +14147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>166</v>
       </c>
@@ -14150,7 +14155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>118</v>
       </c>
@@ -14158,7 +14163,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -14166,7 +14171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>119</v>
       </c>
@@ -14174,7 +14179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>131</v>
       </c>
@@ -14182,7 +14187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>130</v>
       </c>
@@ -14190,7 +14195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>134</v>
       </c>
@@ -14198,7 +14203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>133</v>
       </c>
@@ -14208,6 +14213,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>